--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic Physical Therapy; Elingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Group; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Hamm</t>
+    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic PT; Elingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Grp.; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Hamm</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Learning Resource</t>
+    <t xml:space="preserve">Learning Resources</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
@@ -952,7 +952,7 @@
         <v>40</v>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -968,7 +968,7 @@
         <v>41</v>
       </c>
       <c r="B18" t="n">
-        <v>34.4375</v>
+        <v>34.375</v>
       </c>
     </row>
   </sheetData>
@@ -1107,7 +1107,7 @@
         <v>40</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1123,7 +1123,7 @@
         <v>41</v>
       </c>
       <c r="B18" t="n">
-        <v>11.9375</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1262,7 @@
         <v>40</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -31,13 +31,19 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic PT; Elingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Grp.; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Hamm</t>
+    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic PT; Ellingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Grp.; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Margolin; Flowers Foods; Sripetch; Hikma; Abouammo; Keathley</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais; Zorn</t>
+    <t xml:space="preserve">Callais; Zorn; Rutherford; NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiles; Klein; Fernandez</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
@@ -46,10 +52,16 @@
     <t xml:space="preserve">Bost; R.W.</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiles; Klein</t>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm; Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe; Pitchford</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
@@ -58,10 +70,10 @@
     <t xml:space="preserve">Plaquemines Parish; Rico</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mirabelli</t>
+    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Kavanaugh, Barrett</t>
@@ -80,12 +92,6 @@
   </si>
   <si>
     <t xml:space="preserve">Learning Resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
@@ -553,7 +559,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -564,7 +570,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -575,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -608,7 +614,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -619,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -667,6 +673,17 @@
       </c>
       <c r="C12" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +699,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -690,7 +707,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -698,7 +715,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -706,7 +723,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -714,7 +731,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -722,7 +739,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -730,7 +747,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -738,7 +755,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -746,7 +763,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -754,7 +771,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -762,7 +779,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -770,7 +787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -778,7 +795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -786,7 +803,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -794,7 +811,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -802,18 +819,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>25.6666666666667</v>
+        <v>25.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -829,15 +846,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -845,7 +862,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -853,7 +870,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -861,7 +878,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -869,7 +886,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>39</v>
@@ -877,7 +894,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -885,7 +902,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -893,7 +910,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -901,7 +918,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -909,7 +926,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -917,7 +934,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -925,7 +942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -933,7 +950,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -941,7 +958,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -949,7 +966,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>28</v>
@@ -957,18 +974,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>34.375</v>
+        <v>34.5625</v>
       </c>
     </row>
   </sheetData>
@@ -984,15 +1001,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1000,7 +1017,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1008,7 +1025,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1016,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1024,7 +1041,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1032,7 +1049,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1040,7 +1057,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1048,7 +1065,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1056,7 +1073,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1064,7 +1081,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1072,7 +1089,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1080,7 +1097,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1088,7 +1105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1096,7 +1113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1104,7 +1121,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -1112,18 +1129,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>12.1875</v>
       </c>
     </row>
   </sheetData>
@@ -1139,15 +1156,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1155,7 +1172,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1163,7 +1180,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1171,7 +1188,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1179,7 +1196,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1187,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1195,7 +1212,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1203,7 +1220,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1211,7 +1228,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1219,7 +1236,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1227,7 +1244,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1235,7 +1252,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1243,7 +1260,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>22</v>
@@ -1251,7 +1268,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1259,7 +1276,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>18</v>
@@ -1267,15 +1284,15 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
         <v>23</v>
@@ -1294,33 +1311,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E2" t="n">
         <v>0.06</v>
@@ -1328,16 +1345,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1345,16 +1362,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E4" t="n">
         <v>0.02</v>
@@ -1362,50 +1379,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E6" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
         <v>56</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -1413,33 +1430,33 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E8" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
         <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E9" t="n">
         <v>0.11</v>
@@ -1447,16 +1464,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E10" t="n">
         <v>0.04</v>
@@ -1464,16 +1481,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E11" t="n">
         <v>0.03</v>
@@ -1481,16 +1498,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E12" t="n">
         <v>0.15</v>
@@ -1498,16 +1515,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E13" t="n">
         <v>0.02</v>
@@ -1515,84 +1532,84 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E14" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E16" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -1600,50 +1617,50 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E21" t="n">
         <v>0.07</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais; Zorn; Rutherford; NA</t>
+    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -31,13 +31,13 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic PT; Ellingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Grp.; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Margolin; Flowers Foods; Sripetch; Hikma; Abouammo; Keathley</t>
+    <t xml:space="preserve">Barrett; Berk; Case; Clark; Coney Island Auto; Cox; Dynamic PT; Ellingburg; Enbridge; First Choice; Galette; GEO Group; Hain Celestial Grp.; Jules; Montgomery; Olivier; Pitts; Urias-Orellana; Villarreal; IAM Pension Fund; Margolin; Flowers Foods; Sripetch; Hikma; Abouammo; Keathley; Hemani; Pung</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit</t>
+    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit; McCarthy; Cisco; Exxon; Landor; Lau; Wolford; Al Otro Lado; Mullin v. Doe</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
@@ -46,52 +46,70 @@
     <t xml:space="preserve">Chiles; Klein; Fernandez</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T; Hunter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
     <t xml:space="preserve">Bost; R.W.</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe; Pitchford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquemines Parish; Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito, Thomas, Sotomayor, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMD Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsanto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Resources</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamm; Whitton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe; Pitchford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaquemines Parish; Rico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT\&amp;T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Havana Docks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Resources</t>
+    <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
@@ -559,7 +577,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -570,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -684,6 +702,39 @@
       </c>
       <c r="C13" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -699,7 +750,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -707,7 +758,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -715,7 +766,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -723,7 +774,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -731,7 +782,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -739,7 +790,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -747,7 +798,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -755,7 +806,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -763,7 +814,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -771,7 +822,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -779,7 +830,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -787,7 +838,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -795,7 +846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -803,7 +854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -811,7 +862,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -819,18 +870,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B17" t="n">
-        <v>25.8666666666667</v>
+        <v>26.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -846,15 +897,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -862,7 +913,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -870,7 +921,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -878,7 +929,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -886,7 +937,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" t="n">
         <v>39</v>
@@ -894,7 +945,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -902,7 +953,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -910,7 +961,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -918,7 +969,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -926,7 +977,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -934,7 +985,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -942,7 +993,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -950,7 +1001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -958,7 +1009,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -966,7 +1017,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" t="n">
         <v>28</v>
@@ -974,18 +1025,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" t="n">
-        <v>34.5625</v>
+        <v>35.3125</v>
       </c>
     </row>
   </sheetData>
@@ -1001,15 +1052,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1017,7 +1068,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1025,7 +1076,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1033,7 +1084,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1041,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1049,7 +1100,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1057,7 +1108,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1065,7 +1116,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1073,7 +1124,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1081,7 +1132,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1089,7 +1140,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1097,7 +1148,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1105,7 +1156,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1113,7 +1164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1121,7 +1172,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -1129,18 +1180,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" t="n">
-        <v>12.1875</v>
+        <v>12.875</v>
       </c>
     </row>
   </sheetData>
@@ -1156,15 +1207,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1172,7 +1223,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1180,7 +1231,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1188,7 +1239,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1196,7 +1247,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1204,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1212,7 +1263,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1220,7 +1271,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1228,7 +1279,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1236,7 +1287,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1244,7 +1295,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1252,7 +1303,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1260,7 +1311,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
         <v>22</v>
@@ -1268,7 +1319,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1276,7 +1327,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" t="n">
         <v>18</v>
@@ -1284,15 +1335,15 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" t="n">
         <v>23</v>
@@ -1311,33 +1362,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E2" t="n">
         <v>0.06</v>
@@ -1345,16 +1396,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1362,16 +1413,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E4" t="n">
         <v>0.02</v>
@@ -1379,16 +1430,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
@@ -1396,33 +1447,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -1430,33 +1481,33 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E9" t="n">
         <v>0.11</v>
@@ -1464,16 +1515,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E10" t="n">
         <v>0.04</v>
@@ -1481,16 +1532,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E11" t="n">
         <v>0.03</v>
@@ -1498,16 +1549,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E12" t="n">
         <v>0.15</v>
@@ -1515,16 +1566,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E13" t="n">
         <v>0.02</v>
@@ -1532,33 +1583,33 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E14" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
         <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1566,33 +1617,33 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C16" t="n">
         <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E16" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E17" t="n">
         <v>0.01</v>
@@ -1600,16 +1651,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -1617,16 +1668,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E19" t="n">
         <v>0.03</v>
@@ -1634,16 +1685,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E20" t="n">
         <v>0.14</v>
@@ -1651,16 +1702,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E21" t="n">
         <v>0.07</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit; McCarthy; Cisco; Exxon; Landor; Lau; Wolford; Al Otro Lado; Mullin v. Doe</t>
+    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit; McCarthy; Cisco; Exxon; Landor; Lau; Wolford; Al Otro Lado; Mullin v. Doe; Slaughter</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
@@ -46,6 +46,12 @@
     <t xml:space="preserve">Chiles; Klein; Fernandez</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe; Pitchford; Cook</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
@@ -58,12 +64,6 @@
     <t xml:space="preserve">Bost; R.W.</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe; Pitchford</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
@@ -94,6 +94,12 @@
     <t xml:space="preserve">Monsanto</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
   </si>
   <si>
@@ -104,6 +110,12 @@
   </si>
   <si>
     <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatrie</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
@@ -588,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -610,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -735,6 +747,28 @@
       </c>
       <c r="C16" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +784,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -758,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -766,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -774,7 +808,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -782,7 +816,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -790,7 +824,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -798,7 +832,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -806,7 +840,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -814,7 +848,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -822,7 +856,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -830,7 +864,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -838,7 +872,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -846,7 +880,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -854,7 +888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -862,7 +896,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -870,18 +904,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B17" t="n">
-        <v>26.5333333333333</v>
+        <v>26.8</v>
       </c>
     </row>
   </sheetData>
@@ -897,15 +931,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -913,7 +947,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -921,7 +955,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -929,7 +963,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -937,7 +971,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>39</v>
@@ -945,7 +979,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -953,7 +987,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -961,7 +995,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -969,7 +1003,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -977,7 +1011,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -985,7 +1019,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -993,7 +1027,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -1001,7 +1035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -1009,7 +1043,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -1017,7 +1051,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" t="n">
         <v>28</v>
@@ -1025,18 +1059,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" t="n">
-        <v>35.3125</v>
+        <v>35.625</v>
       </c>
     </row>
   </sheetData>
@@ -1052,15 +1086,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1068,7 +1102,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1076,7 +1110,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1084,7 +1118,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1092,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1100,7 +1134,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1108,7 +1142,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1116,7 +1150,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1124,7 +1158,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1132,7 +1166,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1140,7 +1174,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1148,7 +1182,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1156,7 +1190,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1164,7 +1198,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1172,7 +1206,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -1180,18 +1214,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" t="n">
-        <v>12.875</v>
+        <v>12.9375</v>
       </c>
     </row>
   </sheetData>
@@ -1207,15 +1241,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1223,7 +1257,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1231,7 +1265,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1239,7 +1273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1247,7 +1281,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1255,7 +1289,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1263,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1271,7 +1305,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1279,7 +1313,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1287,7 +1321,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1295,7 +1329,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1303,7 +1337,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1311,7 +1345,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
         <v>22</v>
@@ -1319,7 +1353,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1327,7 +1361,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" t="n">
         <v>18</v>
@@ -1335,15 +1369,15 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" t="n">
         <v>23</v>
@@ -1362,33 +1396,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E2" t="n">
         <v>0.06</v>
@@ -1396,16 +1430,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1413,16 +1447,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E4" t="n">
         <v>0.02</v>
@@ -1430,16 +1464,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
@@ -1447,33 +1481,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
       </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E6" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -1481,33 +1515,33 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E8" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E9" t="n">
         <v>0.11</v>
@@ -1515,16 +1549,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E10" t="n">
         <v>0.04</v>
@@ -1532,16 +1566,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
         <v>66</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E11" t="n">
         <v>0.03</v>
@@ -1549,16 +1583,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" t="n">
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E12" t="n">
         <v>0.15</v>
@@ -1566,16 +1600,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E13" t="n">
         <v>0.02</v>
@@ -1583,16 +1617,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E14" t="n">
         <v>0.36</v>
@@ -1600,16 +1634,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1617,16 +1651,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D16" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E16" t="n">
         <v>0.37</v>
@@ -1634,16 +1668,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E17" t="n">
         <v>0.01</v>
@@ -1651,16 +1685,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C18" t="n">
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -1668,16 +1702,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E19" t="n">
         <v>0.03</v>
@@ -1685,33 +1719,33 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" t="n">
         <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E21" t="n">
         <v>0.07</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit; McCarthy; Cisco; Exxon; Landor; Lau; Wolford; Al Otro Lado; Mullin v. Doe; Slaughter</t>
+    <t xml:space="preserve">Callais; Zorn; Rutherford; FS Credit; McCarthy; Cisco; Exxon; Landor; Lau; Wolford; Al Otro Lado; Mullin v. Doe; Slaughter; B.P.J.; NRSC</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t xml:space="preserve">Chatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
@@ -600,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -769,6 +775,17 @@
       </c>
       <c r="C18" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +801,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -792,7 +809,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -800,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -808,7 +825,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -816,7 +833,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -824,7 +841,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -832,7 +849,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -840,7 +857,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -848,7 +865,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -856,7 +873,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -864,7 +881,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -872,7 +889,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -880,7 +897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -888,7 +905,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -896,7 +913,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -904,18 +921,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -931,15 +948,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -947,7 +964,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -955,7 +972,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -963,7 +980,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -971,7 +988,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>39</v>
@@ -979,7 +996,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -987,7 +1004,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -995,7 +1012,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -1003,7 +1020,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -1011,7 +1028,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -1019,7 +1036,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -1027,7 +1044,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -1035,7 +1052,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -1043,7 +1060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -1051,7 +1068,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
         <v>28</v>
@@ -1059,18 +1076,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" t="n">
-        <v>35.625</v>
+        <v>35.75</v>
       </c>
     </row>
   </sheetData>
@@ -1086,15 +1103,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1102,7 +1119,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1110,7 +1127,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1118,7 +1135,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1126,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1134,7 +1151,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1142,7 +1159,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1150,7 +1167,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1158,7 +1175,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1166,7 +1183,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1174,7 +1191,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1182,7 +1199,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1190,7 +1207,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1198,7 +1215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1206,7 +1223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -1214,18 +1231,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" t="n">
-        <v>12.9375</v>
+        <v>13.0625</v>
       </c>
     </row>
   </sheetData>
@@ -1241,15 +1258,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1257,7 +1274,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1265,7 +1282,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1273,7 +1290,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1281,7 +1298,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1289,7 +1306,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1297,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1305,7 +1322,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1313,7 +1330,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1321,7 +1338,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1329,7 +1346,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1337,7 +1354,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1345,7 +1362,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>22</v>
@@ -1353,7 +1370,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1361,7 +1378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
         <v>18</v>
@@ -1369,15 +1386,15 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" t="n">
         <v>23</v>
@@ -1396,50 +1413,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1447,16 +1464,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E4" t="n">
         <v>0.02</v>
@@ -1464,16 +1481,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
@@ -1481,33 +1498,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E6" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -1515,50 +1532,50 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E10" t="n">
         <v>0.04</v>
@@ -1566,16 +1583,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E11" t="n">
         <v>0.03</v>
@@ -1583,16 +1600,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" t="n">
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E12" t="n">
         <v>0.15</v>
@@ -1600,16 +1617,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E13" t="n">
         <v>0.02</v>
@@ -1617,16 +1634,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E14" t="n">
         <v>0.36</v>
@@ -1634,16 +1651,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1651,16 +1668,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E16" t="n">
         <v>0.37</v>
@@ -1668,16 +1685,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E17" t="n">
         <v>0.01</v>
@@ -1685,16 +1702,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" t="n">
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -1702,16 +1719,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E19" t="n">
         <v>0.03</v>
@@ -1719,16 +1736,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E20" t="n">
         <v>0.13</v>
@@ -1736,16 +1753,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
         <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E21" t="n">
         <v>0.07</v>
